--- a/data/trans_camb/P5_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P5_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 22,42</t>
+          <t>-3,05; 22,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 25,91</t>
+          <t>-1,65; 24,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 2,51</t>
+          <t>-18,66; 2,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,51; 29,75</t>
+          <t>3,86; 29,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 24,2</t>
+          <t>-0,23; 25,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,52; 1,97</t>
+          <t>-18,27; 2,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,3; 22,09</t>
+          <t>3,96; 22,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,5; 21,29</t>
+          <t>3,34; 21,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,49; -0,95</t>
+          <t>-16,0; -1,49</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 102,04</t>
+          <t>-8,93; 102,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 119,44</t>
+          <t>-5,59; 113,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-56,84; 10,94</t>
+          <t>-56,43; 11,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,83; 143,75</t>
+          <t>12,55; 148,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 117,25</t>
+          <t>-0,92; 130,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,36; 12,19</t>
+          <t>-56,57; 13,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,56; 99,36</t>
+          <t>12,38; 95,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,18; 95,03</t>
+          <t>11,54; 92,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-50,06; -4,25</t>
+          <t>-52,14; -6,02</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,02; 31,16</t>
+          <t>5,49; 30,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,57; 28,01</t>
+          <t>4,95; 27,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 9,47</t>
+          <t>-11,13; 9,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,35; 37,05</t>
+          <t>11,4; 36,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 24,05</t>
+          <t>2,29; 23,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,28; 6,28</t>
+          <t>-14,19; 6,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,23; 31,86</t>
+          <t>13,61; 30,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,74; 24,0</t>
+          <t>7,41; 23,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 5,47</t>
+          <t>-9,06; 4,7</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,27; 243,52</t>
+          <t>20,99; 234,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27,88; 236,37</t>
+          <t>19,53; 225,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-44,15; 80,83</t>
+          <t>-47,01; 89,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45,52; 259,13</t>
+          <t>44,3; 256,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,32; 158,45</t>
+          <t>6,88; 163,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,13; 47,68</t>
+          <t>-56,92; 44,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,87; 215,01</t>
+          <t>57,32; 201,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32,6; 170,03</t>
+          <t>33,73; 165,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-37,09; 39,05</t>
+          <t>-39,02; 29,89</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 22,61</t>
+          <t>-2,01; 23,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 26,18</t>
+          <t>-0,09; 27,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,61; 13,03</t>
+          <t>-12,0; 12,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 17,96</t>
+          <t>-8,26; 17,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 17,5</t>
+          <t>-7,54; 16,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-30,02; -8,71</t>
+          <t>-28,92; -8,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 15,92</t>
+          <t>-2,3; 15,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 17,77</t>
+          <t>-1,91; 17,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-18,96; -2,45</t>
+          <t>-18,9; -2,73</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 153,55</t>
+          <t>-8,64; 176,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 181,58</t>
+          <t>-3,99; 217,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-50,25; 91,12</t>
+          <t>-48,33; 89,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,45; 74,83</t>
+          <t>-24,04; 68,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-21,48; 69,86</t>
+          <t>-21,4; 62,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-81,8; -27,03</t>
+          <t>-81,69; -26,31</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 74,87</t>
+          <t>-7,96; 69,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 81,14</t>
+          <t>-6,23; 79,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-64,23; -11,03</t>
+          <t>-62,9; -11,2</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,67; 20,99</t>
+          <t>3,05; 21,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 8,14</t>
+          <t>-8,86; 7,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,58; 24,67</t>
+          <t>-19,67; 20,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 15,21</t>
+          <t>-2,26; 14,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 19,08</t>
+          <t>2,39; 19,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,31; -0,5</t>
+          <t>-16,54; -1,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,36; 15,45</t>
+          <t>2,42; 15,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 11,08</t>
+          <t>-0,46; 12,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-15,02; 8,69</t>
+          <t>-15,23; 8,93</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,8; 73,22</t>
+          <t>8,21; 74,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-22,84; 28,17</t>
+          <t>-24,27; 26,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-58,52; 95,33</t>
+          <t>-59,68; 82,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 65,35</t>
+          <t>-6,83; 64,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,59; 81,35</t>
+          <t>6,09; 83,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-51,04; -0,72</t>
+          <t>-51,67; -5,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,27; 58,45</t>
+          <t>7,35; 56,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 41,8</t>
+          <t>-1,32; 46,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-48,02; 33,88</t>
+          <t>-47,85; 35,39</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 10,73</t>
+          <t>-13,49; 10,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 12,16</t>
+          <t>-10,28; 13,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 3,26</t>
+          <t>-17,72; 5,3</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 11,79</t>
+          <t>-10,13; 12,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 15,17</t>
+          <t>-6,93; 16,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-25,91; -7,98</t>
+          <t>-27,19; -7,38</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 7,27</t>
+          <t>-8,98; 7,69</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 11,41</t>
+          <t>-5,38; 11,15</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-20,8; -6,2</t>
+          <t>-20,51; -5,91</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-35,84; 41,12</t>
+          <t>-34,97; 41,21</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-25,81; 46,8</t>
+          <t>-27,03; 57,38</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-47,24; 13,07</t>
+          <t>-45,96; 22,38</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-27,94; 41,48</t>
+          <t>-25,59; 41,85</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-19,05; 54,48</t>
+          <t>-17,47; 57,72</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-67,48; -28,47</t>
+          <t>-67,93; -26,29</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-24,43; 24,93</t>
+          <t>-24,02; 25,54</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 40,8</t>
+          <t>-14,49; 38,53</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-54,36; -20,88</t>
+          <t>-54,51; -21,28</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 28,59</t>
+          <t>0,95; 28,79</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 21,33</t>
+          <t>-4,99; 21,73</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-29,54; -7,01</t>
+          <t>-30,09; -8,1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4,57; 29,03</t>
+          <t>2,88; 29,11</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 24,39</t>
+          <t>-1,72; 23,71</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-21,29; 2,13</t>
+          <t>-20,7; 2,49</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,29; 24,31</t>
+          <t>5,82; 24,37</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,49; 19,31</t>
+          <t>0,92; 19,31</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-22,76; -6,33</t>
+          <t>-22,64; -6,13</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 119,15</t>
+          <t>2,67; 109,91</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-18,37; 88,07</t>
+          <t>-13,41; 85,93</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-79,76; -27,26</t>
+          <t>-80,95; -30,03</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12,79; 139,04</t>
+          <t>7,99; 133,45</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 110,38</t>
+          <t>-5,24; 107,53</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-63,76; 13,4</t>
+          <t>-62,83; 11,62</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>18,36; 97,52</t>
+          <t>18,11; 98,02</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1,05; 78,59</t>
+          <t>3,49; 78,5</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-66,73; -23,41</t>
+          <t>-66,91; -23,24</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>4,56; 14,87</t>
+          <t>5,42; 15,21</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,24; 11,57</t>
+          <t>2,07; 11,7</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 4,57</t>
+          <t>-11,4; 5,66</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5,27; 14,63</t>
+          <t>5,79; 15,31</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,57; 13,94</t>
+          <t>5,24; 13,85</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-14,9; -6,43</t>
+          <t>-14,61; -6,28</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,05; 13,65</t>
+          <t>7,26; 13,76</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>5,19; 11,55</t>
+          <t>5,19; 11,66</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-12,3; -3,27</t>
+          <t>-11,94; -3,11</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>14,79; 58,37</t>
+          <t>18,01; 59,17</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>7,1; 45,15</t>
+          <t>7,11; 45,2</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-40,22; 19,03</t>
+          <t>-39,54; 21,62</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18,02; 57,28</t>
+          <t>18,84; 59,37</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>15,49; 54,44</t>
+          <t>17,64; 55,02</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-50,08; -25,54</t>
+          <t>-49,46; -24,59</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,88; 51,97</t>
+          <t>24,4; 52,07</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>17,88; 43,55</t>
+          <t>17,61; 44,06</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-41,75; -10,8</t>
+          <t>-41,16; -11,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P5_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P5_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 22,46</t>
+          <t>-3,82; 21,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 24,87</t>
+          <t>-0,7; 24,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,66; 2,64</t>
+          <t>-19,48; 1,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,86; 29,81</t>
+          <t>4,37; 28,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 25,49</t>
+          <t>0,23; 24,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,27; 2,02</t>
+          <t>-18,51; 0,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,96; 22,08</t>
+          <t>4,48; 22,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,34; 21,38</t>
+          <t>2,7; 20,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,0; -1,49</t>
+          <t>-15,5; -1,28</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 102,08</t>
+          <t>-11,07; 99,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 113,8</t>
+          <t>-3,4; 110,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-56,43; 11,9</t>
+          <t>-56,37; 9,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,55; 148,87</t>
+          <t>13,61; 151,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 130,1</t>
+          <t>0,86; 126,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-56,57; 13,32</t>
+          <t>-57,92; 5,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,38; 95,01</t>
+          <t>12,98; 98,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,54; 92,3</t>
+          <t>8,6; 92,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-52,14; -6,02</t>
+          <t>-49,34; -5,45</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,49; 30,84</t>
+          <t>6,55; 30,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,95; 27,86</t>
+          <t>4,56; 27,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 9,91</t>
+          <t>-10,24; 9,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,4; 36,16</t>
+          <t>12,39; 38,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 23,74</t>
+          <t>2,57; 24,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,19; 6,16</t>
+          <t>-13,44; 6,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,61; 30,58</t>
+          <t>14,19; 30,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,41; 23,88</t>
+          <t>7,97; 23,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 4,7</t>
+          <t>-8,47; 5,66</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,99; 234,25</t>
+          <t>26,71; 260,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,53; 225,43</t>
+          <t>17,74; 219,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-47,01; 89,17</t>
+          <t>-42,94; 79,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44,3; 256,63</t>
+          <t>45,91; 282,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,88; 163,6</t>
+          <t>8,02; 162,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,92; 44,23</t>
+          <t>-54,04; 44,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,32; 201,6</t>
+          <t>61,62; 211,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33,73; 165,53</t>
+          <t>31,4; 153,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-39,02; 29,89</t>
+          <t>-36,93; 39,13</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 23,69</t>
+          <t>-0,72; 24,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 27,75</t>
+          <t>1,15; 28,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 12,74</t>
+          <t>-12,78; 12,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 17,21</t>
+          <t>-8,74; 16,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 16,31</t>
+          <t>-8,41; 16,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,92; -8,27</t>
+          <t>-29,52; -7,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 15,87</t>
+          <t>-1,35; 16,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 17,26</t>
+          <t>-0,94; 17,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-18,9; -2,73</t>
+          <t>-18,99; -2,72</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 176,39</t>
+          <t>-2,94; 194,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 217,56</t>
+          <t>2,93; 214,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-48,33; 89,64</t>
+          <t>-52,03; 91,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,04; 68,75</t>
+          <t>-22,88; 71,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-21,4; 62,31</t>
+          <t>-23,15; 69,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-81,69; -26,31</t>
+          <t>-82,92; -27,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 69,79</t>
+          <t>-4,52; 76,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 79,59</t>
+          <t>-2,94; 85,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-62,9; -11,2</t>
+          <t>-62,56; -11,43</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,05; 21,33</t>
+          <t>1,88; 21,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 7,64</t>
+          <t>-8,04; 8,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,67; 20,28</t>
+          <t>-19,81; 21,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 14,31</t>
+          <t>-2,92; 15,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,39; 19,25</t>
+          <t>1,85; 19,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,54; -1,38</t>
+          <t>-16,09; -1,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,42; 15,16</t>
+          <t>2,22; 15,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 12,1</t>
+          <t>-0,63; 11,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-15,23; 8,93</t>
+          <t>-15,39; 6,96</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,21; 74,94</t>
+          <t>5,48; 77,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-24,27; 26,75</t>
+          <t>-22,57; 32,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-59,68; 82,12</t>
+          <t>-58,75; 78,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 64,17</t>
+          <t>-9,2; 66,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,09; 83,3</t>
+          <t>5,48; 82,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-51,67; -5,19</t>
+          <t>-52,04; -3,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,35; 56,28</t>
+          <t>5,87; 56,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 46,18</t>
+          <t>-1,86; 42,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-47,85; 35,39</t>
+          <t>-48,63; 25,98</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 10,17</t>
+          <t>-14,89; 9,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 13,68</t>
+          <t>-10,42; 12,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,72; 5,3</t>
+          <t>-18,81; 4,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 12,2</t>
+          <t>-10,92; 13,77</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 16,12</t>
+          <t>-7,31; 16,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-27,19; -7,38</t>
+          <t>-26,31; -6,13</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 7,69</t>
+          <t>-8,47; 8,56</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 11,15</t>
+          <t>-5,49; 11,6</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-20,51; -5,91</t>
+          <t>-20,96; -5,55</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-34,97; 41,21</t>
+          <t>-38,43; 36,62</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-27,03; 57,38</t>
+          <t>-27,21; 50,66</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-45,96; 22,38</t>
+          <t>-47,54; 15,9</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-25,59; 41,85</t>
+          <t>-26,74; 49,46</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-17,47; 57,72</t>
+          <t>-17,51; 57,82</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-67,93; -26,29</t>
+          <t>-67,31; -22,17</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-24,02; 25,54</t>
+          <t>-23,23; 30,38</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 38,53</t>
+          <t>-14,65; 39,75</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-54,51; -21,28</t>
+          <t>-54,71; -18,36</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,95; 28,79</t>
+          <t>-0,36; 29,04</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 21,73</t>
+          <t>-6,58; 21,8</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-30,09; -8,1</t>
+          <t>-29,3; -7,29</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,88; 29,11</t>
+          <t>1,7; 28,05</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 23,71</t>
+          <t>-1,62; 23,93</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-20,7; 2,49</t>
+          <t>-20,63; 4,12</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,82; 24,37</t>
+          <t>5,04; 24,07</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,92; 19,31</t>
+          <t>-0,18; 18,79</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-22,64; -6,13</t>
+          <t>-21,98; -6,56</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2,67; 109,91</t>
+          <t>-0,57; 112,56</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 85,93</t>
+          <t>-17,03; 82,9</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-80,95; -30,03</t>
+          <t>-79,17; -28,08</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7,99; 133,45</t>
+          <t>2,7; 125,48</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 107,53</t>
+          <t>-4,73; 113,41</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-62,83; 11,62</t>
+          <t>-61,15; 21,76</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>18,11; 98,02</t>
+          <t>15,62; 97,73</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3,49; 78,5</t>
+          <t>-0,57; 74,58</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-66,91; -23,24</t>
+          <t>-65,54; -23,97</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>5,42; 15,21</t>
+          <t>5,3; 15,32</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,07; 11,7</t>
+          <t>2,08; 11,85</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 5,66</t>
+          <t>-11,53; 4,22</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5,79; 15,31</t>
+          <t>5,54; 14,91</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,24; 13,85</t>
+          <t>5,0; 13,97</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-14,61; -6,28</t>
+          <t>-14,7; -6,42</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,26; 13,76</t>
+          <t>6,7; 13,4</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>5,19; 11,66</t>
+          <t>4,66; 11,26</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-11,94; -3,11</t>
+          <t>-12,23; -3,38</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>18,01; 59,17</t>
+          <t>17,03; 59,49</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>7,11; 45,2</t>
+          <t>7,08; 47,36</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-39,54; 21,62</t>
+          <t>-39,29; 16,25</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18,84; 59,37</t>
+          <t>18,4; 58,3</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>17,64; 55,02</t>
+          <t>16,52; 54,74</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-49,46; -24,59</t>
+          <t>-49,18; -25,31</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,4; 52,07</t>
+          <t>23,19; 51,07</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>17,61; 44,06</t>
+          <t>15,18; 42,18</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-41,16; -11,28</t>
+          <t>-41,22; -10,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P5_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P5_R-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>17,13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12,9</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-7,67</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>9,85</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>12,06</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-8,5</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17,13</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>12,9</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-8,52</t>
+          <t>-8,33</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-8,66</t>
+          <t>-8,08</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 21,39</t>
+          <t>3,51; 29,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 24,55</t>
+          <t>-0,63; 24,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,48; 1,5</t>
+          <t>-18,96; 3,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,37; 28,9</t>
+          <t>-2,97; 22,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 24,85</t>
+          <t>0,24; 25,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,51; 0,88</t>
+          <t>-18,75; 2,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,48; 22,96</t>
+          <t>4,3; 22,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,7; 20,66</t>
+          <t>3,5; 21,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,5; -1,28</t>
+          <t>-14,8; -0,21</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>65,37%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>49,24%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-29,26%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>35,41%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>43,38%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-30,58%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>65,37%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>49,24%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-32,5%</t>
+          <t>-29,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-32,02%</t>
+          <t>-29,88%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 99,74</t>
+          <t>8,83; 143,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 110,68</t>
+          <t>-3,53; 117,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-56,37; 9,35</t>
+          <t>-57,55; 17,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,61; 151,6</t>
+          <t>-9,25; 102,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 126,03</t>
+          <t>-2,29; 119,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-57,92; 5,37</t>
+          <t>-56,41; 13,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,98; 98,42</t>
+          <t>14,56; 99,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,6; 92,24</t>
+          <t>11,18; 95,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-49,34; -5,45</t>
+          <t>-47,38; -0,15</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>24,97</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>13,57</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-3,76</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>18,86</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>17,22</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,12</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>24,97</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>13,57</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,67</t>
+          <t>-0,25</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,89</t>
+          <t>-1,98</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,55; 30,56</t>
+          <t>12,35; 37,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,56; 27,12</t>
+          <t>1,36; 24,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 9,58</t>
+          <t>-14,34; 6,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,39; 38,72</t>
+          <t>7,02; 31,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 24,49</t>
+          <t>6,57; 28,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 6,39</t>
+          <t>-11,1; 9,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,19; 30,96</t>
+          <t>13,23; 31,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,97; 23,2</t>
+          <t>7,74; 24,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 5,66</t>
+          <t>-8,62; 5,71</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>123,76%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>67,25%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-18,62%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>104,93%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>95,83%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,65%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>123,76%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>67,25%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-18,21%</t>
+          <t>-1,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-9,91%</t>
+          <t>-10,36%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,71; 260,94</t>
+          <t>45,52; 259,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,74; 219,27</t>
+          <t>4,32; 158,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,94; 79,49</t>
+          <t>-54,26; 49,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45,91; 282,54</t>
+          <t>27,27; 243,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,02; 162,9</t>
+          <t>27,88; 236,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,04; 44,0</t>
+          <t>-45,37; 79,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,62; 211,88</t>
+          <t>57,87; 215,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31,4; 153,03</t>
+          <t>32,6; 170,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-36,93; 39,13</t>
+          <t>-36,88; 39,33</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,5</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4,11</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-18,44</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>11,29</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>13,62</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,11</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,5</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,11</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-19,05</t>
+          <t>-0,58</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-10,96</t>
+          <t>-10,55</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 24,36</t>
+          <t>-8,22; 17,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 28,89</t>
+          <t>-7,0; 17,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,78; 12,39</t>
+          <t>-29,21; -7,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 16,91</t>
+          <t>-2,6; 22,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 16,92</t>
+          <t>-0,4; 26,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-29,52; -7,34</t>
+          <t>-12,48; 12,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 16,13</t>
+          <t>-1,77; 15,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 17,11</t>
+          <t>-1,09; 17,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-18,99; -2,72</t>
+          <t>-18,61; -2,03</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>14,91%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13,61%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-61,1%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>56,55%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>68,22%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-0,57%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>14,91%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>13,61%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-63,14%</t>
+          <t>-2,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-42,16%</t>
+          <t>-40,59%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 194,0</t>
+          <t>-23,45; 74,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,93; 214,41</t>
+          <t>-21,48; 69,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-52,03; 91,83</t>
+          <t>-81,6; -24,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-22,88; 71,66</t>
+          <t>-10,76; 153,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-23,15; 69,53</t>
+          <t>-1,68; 181,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-82,92; -27,4</t>
+          <t>-49,55; 88,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 76,47</t>
+          <t>-6,47; 74,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 85,61</t>
+          <t>-3,97; 81,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-62,56; -11,43</t>
+          <t>-63,3; -8,2</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6,65</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10,71</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-8,68</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>12,04</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,01</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-6,76</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6,65</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>10,71</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-8,73</t>
+          <t>-15,76</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-7,77</t>
+          <t>-12,17</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,88; 21,29</t>
+          <t>-1,97; 15,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 8,8</t>
+          <t>1,84; 19,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,81; 21,78</t>
+          <t>-16,31; -0,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 15,62</t>
+          <t>2,67; 20,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,85; 19,06</t>
+          <t>-8,6; 8,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,09; -1,03</t>
+          <t>-23,26; -6,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,22; 15,45</t>
+          <t>2,36; 15,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 11,32</t>
+          <t>-0,46; 11,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-15,39; 6,96</t>
+          <t>-17,79; -6,57</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>24,12%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>38,86%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-31,49%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>37,39%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>0,03%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-20,99%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>24,12%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>38,86%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-31,68%</t>
+          <t>-48,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-26,0%</t>
+          <t>-40,7%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,48; 77,72</t>
+          <t>-5,98; 65,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-22,57; 32,74</t>
+          <t>5,59; 81,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-58,75; 78,48</t>
+          <t>-51,29; -2,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 66,51</t>
+          <t>6,8; 73,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,48; 82,29</t>
+          <t>-22,84; 28,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-52,04; -3,49</t>
+          <t>-63,44; -22,84</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,87; 56,29</t>
+          <t>7,27; 58,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 42,62</t>
+          <t>-1,36; 41,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-48,63; 25,98</t>
+          <t>-53,45; -23,84</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,02</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4,58</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-17,05</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-1,88</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1,22</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-7,31</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,02</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>4,58</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-17,21</t>
+          <t>-6,49</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-12,98</t>
+          <t>-12,35</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 9,46</t>
+          <t>-10,78; 11,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 12,9</t>
+          <t>-7,49; 15,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-18,81; 4,17</t>
+          <t>-25,68; -7,58</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 13,77</t>
+          <t>-13,28; 10,73</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 16,17</t>
+          <t>-10,43; 12,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-26,31; -6,13</t>
+          <t>-17,28; 3,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 8,56</t>
+          <t>-9,28; 7,27</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 11,6</t>
+          <t>-5,13; 11,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-20,96; -5,55</t>
+          <t>-20,01; -5,18</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>13,47%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-50,1%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-5,8%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>3,77%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-22,55%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>13,47%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-50,59%</t>
+          <t>-20,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-38,97%</t>
+          <t>-37,07%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-38,43; 36,62</t>
+          <t>-27,94; 41,48</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-27,21; 50,66</t>
+          <t>-19,05; 54,48</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-47,54; 15,9</t>
+          <t>-67,1; -27,15</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-26,74; 49,46</t>
+          <t>-35,84; 41,12</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 57,82</t>
+          <t>-25,81; 46,8</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-67,31; -22,17</t>
+          <t>-44,54; 15,11</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-23,23; 30,38</t>
+          <t>-24,43; 24,93</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 39,75</t>
+          <t>-13,57; 40,8</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-54,71; -18,36</t>
+          <t>-52,55; -17,85</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>15,81</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>11,57</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-9,51</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>14,45</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>8,14</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-18,92</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>15,81</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>11,57</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-9,46</t>
+          <t>-19,93</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-14,15</t>
+          <t>-14,8</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 29,04</t>
+          <t>4,57; 29,03</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 21,8</t>
+          <t>-1,96; 24,39</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-29,3; -7,29</t>
+          <t>-21,48; 1,79</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,7; 28,05</t>
+          <t>-0,54; 28,59</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 23,93</t>
+          <t>-7,35; 21,33</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-20,63; 4,12</t>
+          <t>-30,37; -8,37</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,04; 24,07</t>
+          <t>6,29; 24,31</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 18,79</t>
+          <t>0,49; 19,31</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-21,98; -6,56</t>
+          <t>-23,22; -7,06</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>56,57%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>41,41%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-34,05%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>46,42%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>26,15%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-60,8%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>56,57%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>41,41%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-33,84%</t>
+          <t>-64,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-47,86%</t>
+          <t>-50,08%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 112,56</t>
+          <t>12,79; 139,04</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-17,03; 82,9</t>
+          <t>-8,57; 110,38</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-79,17; -28,08</t>
+          <t>-63,72; 10,39</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2,7; 125,48</t>
+          <t>-1,36; 119,15</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 113,41</t>
+          <t>-18,37; 88,07</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-61,15; 21,76</t>
+          <t>-81,79; -33,55</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15,62; 97,73</t>
+          <t>18,36; 97,52</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 74,58</t>
+          <t>1,05; 78,59</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-65,54; -23,97</t>
+          <t>-67,54; -26,23</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>10,43</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>9,49</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-10,49</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>10,03</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>6,83</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-6,52</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>10,43</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>9,49</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-10,74</t>
+          <t>-9,39</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-8,77</t>
+          <t>-9,97</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>5,3; 15,32</t>
+          <t>5,27; 14,63</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,08; 11,85</t>
+          <t>4,57; 13,94</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 4,22</t>
+          <t>-14,86; -6,44</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5,54; 14,91</t>
+          <t>4,56; 14,87</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,0; 13,97</t>
+          <t>2,24; 11,57</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-14,7; -6,42</t>
+          <t>-13,69; -5,22</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,7; 13,4</t>
+          <t>7,05; 13,65</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>4,66; 11,26</t>
+          <t>5,19; 11,55</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-12,23; -3,38</t>
+          <t>-12,82; -7,33</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>37,34%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>33,97%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-37,54%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>35,81%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>24,39%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-23,3%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>37,34%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>33,97%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-38,45%</t>
+          <t>-33,53%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-31,36%</t>
+          <t>-35,64%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>17,03; 59,49</t>
+          <t>18,02; 57,28</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>7,08; 47,36</t>
+          <t>15,49; 54,44</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-39,29; 16,25</t>
+          <t>-49,06; -24,64</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18,4; 58,3</t>
+          <t>14,79; 58,37</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>16,52; 54,74</t>
+          <t>7,1; 45,15</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-49,18; -25,31</t>
+          <t>-44,35; -19,53</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,19; 51,07</t>
+          <t>23,88; 51,97</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>15,18; 42,18</t>
+          <t>17,88; 43,55</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-41,22; -10,75</t>
+          <t>-43,38; -27,38</t>
         </is>
       </c>
     </row>
